--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_4.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_4.xlsx
@@ -513,111 +513,111 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_4_1</t>
+          <t>model_25_4_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9987938355546104</v>
+        <v>0.9998997470464741</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7164594237425985</v>
+        <v>0.7057343180807454</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9986978632665191</v>
+        <v>0.9999255092151573</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9950562300362051</v>
+        <v>0.9999599685445548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9966112870374917</v>
+        <v>0.9999623699029485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007160313183742851</v>
+        <v>5.951448391509293e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1683219343815282</v>
+        <v>0.1746888204028451</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003308845000060878</v>
+        <v>3.02535855787494e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003673433966515033</v>
+        <v>2.061388756438866e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002002159123848315</v>
+        <v>2.543373657156904e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007710307800280669</v>
+        <v>0.001840665990886472</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02675876152541977</v>
+        <v>0.007714563105911633</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000851410196746</v>
+        <v>1.000070766790724</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02789793740182949</v>
+        <v>0.008042988028677454</v>
       </c>
       <c r="P2" t="n">
-        <v>130.483573302428</v>
+        <v>135.4585816957837</v>
       </c>
       <c r="Q2" t="n">
-        <v>201.1783711447837</v>
+        <v>206.1533795381393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_4_0</t>
+          <t>model_25_4_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9987938629385732</v>
+        <v>0.999901360761672</v>
       </c>
       <c r="C3" t="n">
-        <v>0.716458487329944</v>
+        <v>0.7046357704099384</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9986980510126616</v>
+        <v>0.9999245829003263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9950563628308896</v>
+        <v>0.9998567259308608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9966114107286328</v>
+        <v>0.9999227625329393</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007160150620710625</v>
+        <v>5.855651286471668e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1683224902765309</v>
+        <v>0.1753409657550246</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003308367920450914</v>
+        <v>3.062979781862627e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00367333529434621</v>
+        <v>7.377787090892536e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002002086043198115</v>
+        <v>5.220388849879616e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007709693019898664</v>
+        <v>0.001965466304451539</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0267584577670512</v>
+        <v>0.007652222740140062</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000851390866889</v>
+        <v>1.000069627697643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02789762071183831</v>
+        <v>0.007977993704472641</v>
       </c>
       <c r="P3" t="n">
-        <v>130.4836187096256</v>
+        <v>135.4910364763189</v>
       </c>
       <c r="Q3" t="n">
-        <v>201.1784165519812</v>
+        <v>206.1858343186746</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.998849091833691</v>
+        <v>0.9998937556813348</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7155726080508399</v>
+        <v>0.7035113243289379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9986932495109569</v>
+        <v>0.9999181557513634</v>
       </c>
       <c r="E4" t="n">
-        <v>0.995214026036921</v>
+        <v>0.9997128100511323</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9967095184937411</v>
+        <v>0.999866006225987</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006832288041650907</v>
+        <v>6.307121707529647e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1688483864845993</v>
+        <v>0.176008485522248</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003320568962399735</v>
+        <v>3.324011131691798e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00355618474313796</v>
+        <v>0.0001478862372039989</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001944120863141531</v>
+        <v>9.056480364136793e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007572368618060962</v>
+        <v>0.002126491667659252</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02613864579822548</v>
+        <v>0.007941738920116705</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000812405764453</v>
+        <v>1.000074995989646</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02725142206431203</v>
+        <v>0.008279835187612003</v>
       </c>
       <c r="P4" t="n">
-        <v>130.5773615114309</v>
+        <v>135.3424920805215</v>
       </c>
       <c r="Q4" t="n">
-        <v>201.2721593537865</v>
+        <v>206.0372899228771</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9988939598086903</v>
+        <v>0.9998794551804757</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7147828577988554</v>
+        <v>0.7024027472208693</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9986316075198869</v>
+        <v>0.9999028810025931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9953609843512359</v>
+        <v>0.9995450501571252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.99678867188186</v>
+        <v>0.9997975133371978</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006565932360099199</v>
+        <v>7.156061213468453e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1693172163496118</v>
+        <v>0.1766665847816351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003477206732229703</v>
+        <v>3.944377691250628e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003446988387437873</v>
+        <v>0.0002342728937574897</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001897354530330422</v>
+        <v>0.000136858335334998</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007437090953861711</v>
+        <v>0.002314997205199893</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02562407532009536</v>
+        <v>0.008459350574050265</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000780734252689</v>
+        <v>1.000085090460841</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02671494525562017</v>
+        <v>0.008819482641257349</v>
       </c>
       <c r="P5" t="n">
-        <v>130.6568917089764</v>
+        <v>135.0899314904288</v>
       </c>
       <c r="Q5" t="n">
-        <v>201.351689551332</v>
+        <v>205.7847293327844</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9989291222063829</v>
+        <v>0.9998603678072011</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7140737685853358</v>
+        <v>0.7013467941506675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.998524829554017</v>
+        <v>0.9998766344124215</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9954936997130786</v>
+        <v>0.9993656031227355</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9968491627777639</v>
+        <v>0.9997212663370167</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006357193178031562</v>
+        <v>8.289170144205708e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1697381623378162</v>
+        <v>0.1772934441389044</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003748539019692843</v>
+        <v>5.010353118393214e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003348375158739608</v>
+        <v>0.000326677752625109</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001861614589980338</v>
+        <v>0.000188392779009756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007318496154186188</v>
+        <v>0.002520185414443434</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02521347492518943</v>
+        <v>0.009104487983519836</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000755913736671</v>
+        <v>1.000098563900799</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02628686475184311</v>
+        <v>0.009492084885866583</v>
       </c>
       <c r="P6" t="n">
-        <v>130.7215068324904</v>
+        <v>134.7959512081316</v>
       </c>
       <c r="Q6" t="n">
-        <v>201.4163046748461</v>
+        <v>205.4907490504872</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9989566869107082</v>
+        <v>0.9998379950964409</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7134369914641596</v>
+        <v>0.7003689691722232</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9983905280692086</v>
+        <v>0.9998390824983483</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9956130736911788</v>
+        <v>0.9991829491699457</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9968953459157819</v>
+        <v>0.9996404073620797</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0006193557185824088</v>
+        <v>9.617310900011781e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1701161807442857</v>
+        <v>0.1778739232859485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004089811011399095</v>
+        <v>6.535481425815991e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003259675152654591</v>
+        <v>0.0004207339892553705</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00183432812689725</v>
+        <v>0.0002430444017567652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007243874695859387</v>
+        <v>0.002730950466460594</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02488685835099338</v>
+        <v>0.009806788924011663</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000736456298324</v>
+        <v>1.000114356402512</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02594634343389401</v>
+        <v>0.01022428423135851</v>
       </c>
       <c r="P7" t="n">
-        <v>130.7736615676134</v>
+        <v>134.4987215431847</v>
       </c>
       <c r="Q7" t="n">
-        <v>201.4684594099691</v>
+        <v>205.1935193855403</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9989782881993</v>
+        <v>0.9998135989746567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7128650479851064</v>
+        <v>0.6994829182241274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9982410474264101</v>
+        <v>0.9997917688868148</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9957201315707803</v>
+        <v>0.9990028599745866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9969305204841858</v>
+        <v>0.9995575893538768</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006065322605472023</v>
+        <v>0.0001106557007487753</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1704557111001235</v>
+        <v>0.1783999214041462</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004469654590657964</v>
+        <v>8.457069980151429e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003180126538096982</v>
+        <v>0.000513469523934566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001813545875984735</v>
+        <v>0.0002990201118680402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00717216162527</v>
+        <v>0.002937284831128735</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02462787568076472</v>
+        <v>0.01051930134318698</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000721208329906</v>
+        <v>1.00013157719436</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02567633533522569</v>
+        <v>0.01096712977932216</v>
       </c>
       <c r="P8" t="n">
-        <v>130.8155052793112</v>
+        <v>134.2181739444902</v>
       </c>
       <c r="Q8" t="n">
-        <v>201.5103031216669</v>
+        <v>204.9129717868458</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9989952020094983</v>
+        <v>0.9997881889318022</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7123514029643743</v>
+        <v>0.6986908855277951</v>
       </c>
       <c r="D9" t="n">
-        <v>0.998085042423423</v>
+        <v>0.9997372502966533</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9958159293284001</v>
+        <v>0.9988288332277855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9969572111090202</v>
+        <v>0.9994749192938051</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005964914921749316</v>
+        <v>0.0001257401998439045</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1707606329727397</v>
+        <v>0.1788701062267201</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0004866077148171083</v>
+        <v>0.000106712805520568</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003108944679043371</v>
+        <v>0.0006030832477391114</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001797776208082906</v>
+        <v>0.0003548958255910602</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007103975370206616</v>
+        <v>0.003132688933204025</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02442317530901606</v>
+        <v>0.01121339377012617</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000709269169766</v>
+        <v>1.000149513695198</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02546292044486349</v>
+        <v>0.01169077115784556</v>
       </c>
       <c r="P9" t="n">
-        <v>130.8488911588735</v>
+        <v>133.9625853713366</v>
       </c>
       <c r="Q9" t="n">
-        <v>201.5436890012292</v>
+        <v>204.6573832136922</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9990084448292246</v>
+        <v>0.9997626379832325</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7118901206007922</v>
+        <v>0.6979899069190234</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9979286257127739</v>
+        <v>0.9996785956086366</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9959015547837859</v>
+        <v>0.9986633479008339</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9969774171918379</v>
+        <v>0.9993942549564802</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005886299823253668</v>
+        <v>0.0001409083466584001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1710344701101226</v>
+        <v>0.1792862374095862</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005263545891391234</v>
+        <v>0.0001305347403714028</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003045321278578515</v>
+        <v>0.0006882986336251678</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001785837813324137</v>
+        <v>0.0004094158950831041</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007039673982903799</v>
+        <v>0.003312434216529093</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02426169784506779</v>
+        <v>0.01187048215778955</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000699921297018</v>
+        <v>1.000167549658895</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02529456855097051</v>
+        <v>0.01237583315853225</v>
       </c>
       <c r="P10" t="n">
-        <v>130.8754255701818</v>
+        <v>133.7348018052848</v>
       </c>
       <c r="Q10" t="n">
-        <v>201.5702234125374</v>
+        <v>204.4295996476404</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9990187666051092</v>
+        <v>0.9997375577072082</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7114758505759129</v>
+        <v>0.6973723938872003</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9977757236698915</v>
+        <v>0.9996184591607492</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9959778849698553</v>
+        <v>0.998507565054328</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9969925336854478</v>
+        <v>0.9993168375323067</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000582502530282752</v>
+        <v>0.0001557970819179989</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1712803986924242</v>
+        <v>0.1796528198204504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.000565208355190075</v>
+        <v>0.0001549584751515195</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002988604663478896</v>
+        <v>0.0007685178024418617</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001776906509334486</v>
+        <v>0.000461741414461395</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006979795227891311</v>
+        <v>0.003474842100587525</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02413508919152262</v>
+        <v>0.0124818701290311</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00069263533757</v>
+        <v>1.000185253383147</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02516256990492789</v>
+        <v>0.01301324918145712</v>
       </c>
       <c r="P11" t="n">
-        <v>130.8963540574016</v>
+        <v>133.5339123087385</v>
       </c>
       <c r="Q11" t="n">
-        <v>201.5911518997572</v>
+        <v>204.2287101510942</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9990267982179504</v>
+        <v>0.9997134048107622</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7111037164236794</v>
+        <v>0.6968295360487431</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9976289684904858</v>
+        <v>0.9995590019343972</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9960459209161555</v>
+        <v>0.9983621134032094</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9970037561665189</v>
+        <v>0.9992435705830103</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0005777346179526181</v>
+        <v>0.0001701352845991128</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1715013136005483</v>
+        <v>0.1799750836835962</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0006025001486802752</v>
+        <v>0.0001791063518253464</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002938051025685604</v>
+        <v>0.0008434170023054273</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001770275911488834</v>
+        <v>0.0005112616770653869</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006924103630014473</v>
+        <v>0.003619824481943985</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02403611070769599</v>
+        <v>0.01304359170624076</v>
       </c>
       <c r="N12" t="n">
-        <v>1.0006869659638</v>
+        <v>1.000202302486521</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02505937770213106</v>
+        <v>0.01359888440913256</v>
       </c>
       <c r="P12" t="n">
-        <v>130.9127918664371</v>
+        <v>133.3578332912578</v>
       </c>
       <c r="Q12" t="n">
-        <v>201.6075897087927</v>
+        <v>204.0526311336134</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9990330546736397</v>
+        <v>0.999690494480167</v>
       </c>
       <c r="C13" t="n">
-        <v>0.71076949202689</v>
+        <v>0.696352505590462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9974900618773488</v>
+        <v>0.9995017535145995</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9961066516994461</v>
+        <v>0.9982272895733433</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9970120736553839</v>
+        <v>0.9991750102060413</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005740205155906516</v>
+        <v>0.000183735846515193</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1716997236402247</v>
+        <v>0.1802582695702746</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006377975518281883</v>
+        <v>0.0002023571468230841</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002892925438575606</v>
+        <v>0.0009128434880265799</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001765361675198349</v>
+        <v>0.000557600823219895</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006872477910353902</v>
+        <v>0.0037479990600542</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02395872524970082</v>
+        <v>0.01355491964252068</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000682549642137</v>
+        <v>1.000218474484588</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02497869778497904</v>
+        <v>0.01413198063425467</v>
       </c>
       <c r="P13" t="n">
-        <v>130.9256908416726</v>
+        <v>133.2040228972112</v>
       </c>
       <c r="Q13" t="n">
-        <v>201.6204886840282</v>
+        <v>203.8988207395669</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9990379004082101</v>
+        <v>0.9996689520309376</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7104691885686063</v>
+        <v>0.6959324249948959</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9973597889326234</v>
+        <v>0.9994475040533211</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9961608180206251</v>
+        <v>0.9981027446888285</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9970181200112249</v>
+        <v>0.9991112664112234</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000571143878224848</v>
+        <v>0.0001965243749630313</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1718779967454958</v>
+        <v>0.1805076475583395</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0006709010632117679</v>
+        <v>0.0002243899489053281</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002852677529486609</v>
+        <v>0.0009769769105454585</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001761789296349188</v>
+        <v>0.0006006844985888167</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006825069810231408</v>
+        <v>0.003861155511324944</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02389861665923047</v>
+        <v>0.01401871516805414</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000679129123616</v>
+        <v>1.000233680919338</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02491603024737043</v>
+        <v>0.01461552089549918</v>
       </c>
       <c r="P14" t="n">
-        <v>130.9357388083469</v>
+        <v>133.0694481774692</v>
       </c>
       <c r="Q14" t="n">
-        <v>201.6305366507025</v>
+        <v>203.7642460198248</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9990416255000872</v>
+        <v>0.9996489155067635</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7101993824769777</v>
+        <v>0.6955625001554437</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9972386471770203</v>
+        <v>0.9993970055691769</v>
       </c>
       <c r="E15" t="n">
-        <v>0.996209048913955</v>
+        <v>0.9979883500977292</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9970223974012246</v>
+        <v>0.9990525161481447</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0005689325027709702</v>
+        <v>0.000208418921245624</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1720381652965029</v>
+        <v>0.1807272509229594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0007016842584031493</v>
+        <v>0.0002448993342592079</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002816839898874518</v>
+        <v>0.001035883518178697</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001759262078638834</v>
+        <v>0.000640393105043004</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006781442577439773</v>
+        <v>0.003960322008245809</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02385230602627281</v>
+        <v>0.01443672127754858</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000676499646997</v>
+        <v>1.000247824348167</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02486774807489154</v>
+        <v>0.01505132239046673</v>
       </c>
       <c r="P15" t="n">
-        <v>130.9434975103569</v>
+        <v>132.9519209185625</v>
       </c>
       <c r="Q15" t="n">
-        <v>201.6382953527125</v>
+        <v>203.6467187609181</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.999044473711406</v>
+        <v>0.9996303721399356</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7099571357577596</v>
+        <v>0.695236118828257</v>
       </c>
       <c r="D16" t="n">
-        <v>0.997126522050462</v>
+        <v>0.9993503732636697</v>
       </c>
       <c r="E16" t="n">
-        <v>0.996252061158108</v>
+        <v>0.9978835279918673</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9970253322130143</v>
+        <v>0.9989985782365399</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0005672416814958155</v>
+        <v>0.0002194270648264296</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1721819734135441</v>
+        <v>0.1809210049777166</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0007301762481346423</v>
+        <v>0.0002638385151038846</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002784879949320885</v>
+        <v>0.001089860848767169</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001757528098727764</v>
+        <v>0.0006768491001763399</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006741540294774211</v>
+        <v>0.004047444113872778</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02381683609331465</v>
+        <v>0.01481307074263907</v>
       </c>
       <c r="N16" t="n">
-        <v>1.00067448914489</v>
+        <v>1.000260913783575</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02483076811345447</v>
+        <v>0.01544369383143691</v>
       </c>
       <c r="P16" t="n">
-        <v>130.9494501980584</v>
+        <v>132.8489813187219</v>
       </c>
       <c r="Q16" t="n">
-        <v>201.644248040414</v>
+        <v>203.5437791610775</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.999046648684631</v>
+        <v>0.9996133094698157</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7097392982730428</v>
+        <v>0.6949475185609135</v>
       </c>
       <c r="D17" t="n">
-        <v>0.997023311563653</v>
+        <v>0.9993076823809434</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9962904824441988</v>
+        <v>0.9977877624273591</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9970272976124885</v>
+        <v>0.9989492761864344</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005659505234354922</v>
+        <v>0.0002295562028785287</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1723112911545613</v>
+        <v>0.1810923305632941</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0007564029487914396</v>
+        <v>0.0002811769318854954</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002756331279298431</v>
+        <v>0.001139174583612962</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001756366878366802</v>
+        <v>0.0007101717714707342</v>
       </c>
       <c r="L17" t="n">
-        <v>0.006704995959507279</v>
+        <v>0.0041237701888029</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02378971465645379</v>
+        <v>0.01515111226539255</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000672953869672</v>
+        <v>1.000272958021307</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02480249206087733</v>
+        <v>0.01579612648165644</v>
       </c>
       <c r="P17" t="n">
-        <v>130.9540077960138</v>
+        <v>132.7587253314562</v>
       </c>
       <c r="Q17" t="n">
-        <v>201.6488056383694</v>
+        <v>203.4535231738118</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9990482767173439</v>
+        <v>0.9995976728523628</v>
       </c>
       <c r="C18" t="n">
-        <v>0.709543622735902</v>
+        <v>0.6946921584949028</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9969286248549959</v>
+        <v>0.9992688485395326</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9963247315405027</v>
+        <v>0.9977004538229447</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9970284720939311</v>
+        <v>0.9989043445300599</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005649840528898107</v>
+        <v>0.0002388387744652606</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1724274526061512</v>
+        <v>0.1812439233294585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0007804636817741202</v>
+        <v>0.0002969488551771586</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002730882725946135</v>
+        <v>0.001184133472436479</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001755672957470563</v>
+        <v>0.0007405405454440228</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006671753691157356</v>
+        <v>0.004190654320911018</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02376939319565838</v>
+        <v>0.01545440954761005</v>
       </c>
       <c r="N18" t="n">
-        <v>1.00067180467011</v>
+        <v>1.000283995633626</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02478130547342463</v>
+        <v>0.01611233575708986</v>
       </c>
       <c r="P18" t="n">
-        <v>130.9574261043799</v>
+        <v>132.6794436349883</v>
       </c>
       <c r="Q18" t="n">
-        <v>201.6522239467355</v>
+        <v>203.374241477344</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9990494829900478</v>
+        <v>0.9995833974778038</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7093678040607718</v>
+        <v>0.6944659220066087</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9968419711876069</v>
+        <v>0.9992337186850564</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9963553206312007</v>
+        <v>0.9976210209765002</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9970290714334814</v>
+        <v>0.9988635299689607</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0005642679573044767</v>
+        <v>0.0002473132534675695</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1725318261666798</v>
+        <v>0.1813782270818173</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000802483147680022</v>
+        <v>0.0003112164462759571</v>
       </c>
       <c r="J19" t="n">
-        <v>0.002708153714362348</v>
+        <v>0.001225036800764688</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001755318848650461</v>
+        <v>0.0007681266235203227</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006641512928707237</v>
+        <v>0.00424912061570553</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02375432502312951</v>
+        <v>0.01572619640814554</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000670953183496</v>
+        <v>1.000294072368609</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02476559581759579</v>
+        <v>0.0163956931469547</v>
       </c>
       <c r="P19" t="n">
-        <v>130.9599626353751</v>
+        <v>132.6097095844036</v>
       </c>
       <c r="Q19" t="n">
-        <v>201.6547604777307</v>
+        <v>203.3045074267592</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9990503605254676</v>
+        <v>0.9995704011476155</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7092097076603068</v>
+        <v>0.6942653308910337</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9967629515500991</v>
+        <v>0.9992020216497722</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9963826191810313</v>
+        <v>0.9975489068768634</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9970292446745166</v>
+        <v>0.9988265356917063</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0005637470143717451</v>
+        <v>0.0002550284364795571</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1726256790194047</v>
+        <v>0.1814973066331077</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0008225627388436297</v>
+        <v>0.00032408983687838</v>
       </c>
       <c r="J20" t="n">
-        <v>0.002687869716336756</v>
+        <v>0.001262171397176157</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00175521649235084</v>
+        <v>0.0007931306170272684</v>
       </c>
       <c r="L20" t="n">
-        <v>0.006613927020512123</v>
+        <v>0.004300468947037612</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02374335726833392</v>
+        <v>0.01596960977856244</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000670333746729</v>
+        <v>1.000303246248742</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02475416114277217</v>
+        <v>0.01664946912848539</v>
       </c>
       <c r="P20" t="n">
-        <v>130.9618099263521</v>
+        <v>132.5482710068343</v>
       </c>
       <c r="Q20" t="n">
-        <v>201.6566077687077</v>
+        <v>203.2430688491899</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9990509950305639</v>
+        <v>0.9995585904226247</v>
       </c>
       <c r="C21" t="n">
-        <v>0.709067753304627</v>
+        <v>0.6940869120547631</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9966910028756362</v>
+        <v>0.9991734545758799</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9964070689500998</v>
+        <v>0.9974835207688537</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9970291465815098</v>
+        <v>0.9987930428017263</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0005633703447373792</v>
+        <v>0.0002620397930308473</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1727099492570451</v>
+        <v>0.1816032237616103</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0008408455355451324</v>
+        <v>0.000335692029237621</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002669702485088676</v>
+        <v>0.001295841466470344</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001755274448811268</v>
+        <v>0.0008157680643770765</v>
       </c>
       <c r="L21" t="n">
-        <v>0.006588971458783765</v>
+        <v>0.004345630374507703</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02373542383732339</v>
+        <v>0.01618764322039646</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000669885860778</v>
+        <v>1.000311583231088</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02474588996917905</v>
+        <v>0.01687678470532973</v>
       </c>
       <c r="P21" t="n">
-        <v>130.9631466803124</v>
+        <v>132.4940283678778</v>
       </c>
       <c r="Q21" t="n">
-        <v>201.6579445226681</v>
+        <v>203.1888262102335</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9990514337574858</v>
+        <v>0.9995478663713541</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7089400833862339</v>
+        <v>0.6939281655054311</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9966256745764366</v>
+        <v>0.9991477707093284</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9964289073803932</v>
+        <v>0.9974242257837259</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9970288317211442</v>
+        <v>0.9987627403985867</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005631098974844711</v>
+        <v>0.000268406053120042</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1727857396356566</v>
+        <v>0.1816974625707877</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0008574460361385653</v>
+        <v>0.0003461232397068323</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002653475590997188</v>
+        <v>0.00132637495926904</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001755460478304016</v>
+        <v>0.0008362490994879361</v>
       </c>
       <c r="L22" t="n">
-        <v>0.006566285694543954</v>
+        <v>0.004385304201626387</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02372993673578737</v>
+        <v>0.01638310267074103</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000669576171187</v>
+        <v>1.000319153149632</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02474016927037079</v>
+        <v>0.01708056526913232</v>
       </c>
       <c r="P22" t="n">
-        <v>130.9640714981576</v>
+        <v>132.4460192010257</v>
       </c>
       <c r="Q22" t="n">
-        <v>201.6588693405132</v>
+        <v>203.1408170433813</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9990517160529601</v>
+        <v>0.9995381443533193</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7088253527366266</v>
+        <v>0.6937866828232052</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9965663185699899</v>
+        <v>0.9991246872707674</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9964484377260747</v>
+        <v>0.9973705285536713</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9970283482227936</v>
+        <v>0.9987353497359547</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0005629423146964907</v>
+        <v>0.0002741774629947132</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1728538487053695</v>
+        <v>0.1817814528026906</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0008725289241414193</v>
+        <v>0.0003554983159049448</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002638963703160625</v>
+        <v>0.001354025931499723</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001755746144468332</v>
+        <v>0.0008547621237023338</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00654571530019894</v>
+        <v>0.004420349073043762</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02372640543142789</v>
+        <v>0.01655830495536041</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000669376903793</v>
+        <v>1.000326015750598</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02473648763107391</v>
+        <v>0.01726322627772667</v>
       </c>
       <c r="P23" t="n">
-        <v>130.9646667912973</v>
+        <v>132.4034699721281</v>
       </c>
       <c r="Q23" t="n">
-        <v>201.6594646336529</v>
+        <v>203.0982678144837</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9990518971261537</v>
+        <v>0.9995293415964415</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7087221419366891</v>
+        <v>0.6936605660656062</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9965125342518343</v>
+        <v>0.999103932512078</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9964659714807416</v>
+        <v>0.9973219680376991</v>
       </c>
       <c r="F24" t="n">
-        <v>0.997027807395209</v>
+        <v>0.9987106154876729</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005628348218267552</v>
+        <v>0.0002794031597367644</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1729151190946868</v>
+        <v>0.1818563211579616</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0008861959967026164</v>
+        <v>0.0003639276252416846</v>
       </c>
       <c r="J24" t="n">
-        <v>0.002625935368423091</v>
+        <v>0.001379031792645348</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001756065682562854</v>
+        <v>0.0008714797089435164</v>
       </c>
       <c r="L24" t="n">
-        <v>0.006527057495764722</v>
+        <v>0.004451321459465396</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02372414006506358</v>
+        <v>0.01671535700297078</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000669249087421</v>
+        <v>1.000332229461335</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02473412582337352</v>
+        <v>0.01742696435614637</v>
       </c>
       <c r="P24" t="n">
-        <v>130.9650487243339</v>
+        <v>132.3657096043952</v>
       </c>
       <c r="Q24" t="n">
-        <v>201.6598465666895</v>
+        <v>203.0605074467508</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9990519749467693</v>
+        <v>0.9995213840468071</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7086293632363924</v>
+        <v>0.6935480157411562</v>
       </c>
       <c r="D25" t="n">
-        <v>0.99646378541338</v>
+        <v>0.9990853196905763</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9964816012791644</v>
+        <v>0.9972780944251859</v>
       </c>
       <c r="F25" t="n">
-        <v>0.997027152471661</v>
+        <v>0.9986883101975327</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0005627886241476685</v>
+        <v>0.0002841271049479064</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1729701965390141</v>
+        <v>0.1819231358924761</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0008985835091835147</v>
+        <v>0.0003714870111355414</v>
       </c>
       <c r="J25" t="n">
-        <v>0.002614321755160996</v>
+        <v>0.001401624169198569</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001756452632172255</v>
+        <v>0.0008865555901670553</v>
       </c>
       <c r="L25" t="n">
-        <v>0.006510252959104747</v>
+        <v>0.004478550797406414</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02372316640222524</v>
+        <v>0.01685607027002161</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000669194155222</v>
+        <v>1.000337846555195</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02473311070969239</v>
+        <v>0.01757366807829217</v>
       </c>
       <c r="P25" t="n">
-        <v>130.9652128917711</v>
+        <v>132.3321777345828</v>
       </c>
       <c r="Q25" t="n">
-        <v>201.6600107341268</v>
+        <v>203.0269755769384</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9990519946968757</v>
+        <v>0.9995141979500582</v>
       </c>
       <c r="C26" t="n">
-        <v>0.70854596145344</v>
+        <v>0.6934474027244126</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9964197084570832</v>
+        <v>0.999068633515351</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9964956165055474</v>
+        <v>0.9972384910362672</v>
       </c>
       <c r="F26" t="n">
-        <v>0.997026486433883</v>
+        <v>0.9986682038654865</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005627768996313531</v>
+        <v>0.0002883930824012503</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1730197074401441</v>
+        <v>0.181982864125471</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0009097838549467996</v>
+        <v>0.0003782639115431099</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002603907838449558</v>
+        <v>0.001422017627224539</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001756846148421259</v>
+        <v>0.0009001452216788776</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00649501044191661</v>
+        <v>0.00450275018752687</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02372291928982083</v>
+        <v>0.01698214010074261</v>
       </c>
       <c r="N26" t="n">
-        <v>1.00066918021397</v>
+        <v>1.000342919094076</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02473285307720133</v>
+        <v>0.01770510496270749</v>
       </c>
       <c r="P26" t="n">
-        <v>130.9652545579951</v>
+        <v>132.3023722779344</v>
       </c>
       <c r="Q26" t="n">
-        <v>201.6600524003508</v>
+        <v>202.99717012029</v>
       </c>
     </row>
   </sheetData>
